--- a/output/pdf_financials_xlsx/GURN.xlsx
+++ b/output/pdf_financials_xlsx/GURN.xlsx
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.197088</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.4065</v>
@@ -3931,7 +3931,11 @@
           <t>Exploration and evaluation expenditures (Note 5)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>-0.1</v>
       </c>

--- a/output/pdf_financials_xlsx/GURN.xlsx
+++ b/output/pdf_financials_xlsx/GURN.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8.4e-05</v>
+        <v>0.158753</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.364882</v>
+        <v>4.611293</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.020381</v>
+        <v>5.436642</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-8.4e-05</v>
+        <v>-0.158753</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.364882</v>
+        <v>-4.611293</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-1.020381</v>
+        <v>-5.436642</v>
       </c>
     </row>
     <row r="12">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.019916</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.791732</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.744178</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.019916</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.791732</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.744178</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.019916</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.791732</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.833846</v>
+        <v>0.089668</v>
       </c>
     </row>
     <row r="49">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4373,17 +4373,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>-0.158753</v>
+        <v>0.158753</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>-4.611293</v>
+        <v>4.611293</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-5.436642</v>
+        <v>5.436642</v>
       </c>
     </row>
     <row r="59">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">

--- a/output/pdf_financials_xlsx/GURN.xlsx
+++ b/output/pdf_financials_xlsx/GURN.xlsx
@@ -2066,10 +2066,10 @@
         <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.04407</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.051703</v>
       </c>
     </row>
     <row r="102">
@@ -2146,10 +2146,10 @@
         <v>0.158669</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.169849</v>
+        <v>0.125779</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.50039</v>
+        <v>0.448687</v>
       </c>
     </row>
     <row r="107">
@@ -3371,7 +3371,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -3590,7 +3594,11 @@
           <t>Proceeds from private placement (Note 6)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
